--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/44.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/44.xlsx
@@ -426,13 +426,13 @@
         <v>-9.732425414154799</v>
       </c>
       <c r="E2">
-        <v>-7.196258992458667</v>
+        <v>-5.029112471347941</v>
       </c>
       <c r="F2">
-        <v>-0.8457235038704686</v>
+        <v>-0.7586596047340322</v>
       </c>
       <c r="G2">
-        <v>-7.10179999424058</v>
+        <v>-5.342195381934856</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.500934618383825</v>
       </c>
       <c r="E3">
-        <v>-8.256483441030481</v>
+        <v>-7.181079547584956</v>
       </c>
       <c r="F3">
-        <v>-0.9713719282619032</v>
+        <v>-0.7825016753214076</v>
       </c>
       <c r="G3">
-        <v>-6.481479902728563</v>
+        <v>-4.621446580943508</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.242613221960461</v>
       </c>
       <c r="E4">
-        <v>-9.216062554781823</v>
+        <v>-7.690025684359012</v>
       </c>
       <c r="F4">
-        <v>-1.187806934897955</v>
+        <v>-1.00592893120449</v>
       </c>
       <c r="G4">
-        <v>-6.068227813606881</v>
+        <v>-5.109619626164437</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-8.973935739017474</v>
       </c>
       <c r="E5">
-        <v>-9.889682120370804</v>
+        <v>-8.566077095038873</v>
       </c>
       <c r="F5">
-        <v>-1.130783779624043</v>
+        <v>-1.189065224982808</v>
       </c>
       <c r="G5">
-        <v>-5.79455163496641</v>
+        <v>-4.217136275323396</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.688585509673121</v>
       </c>
       <c r="E6">
-        <v>-10.17888858439666</v>
+        <v>-8.785907337267224</v>
       </c>
       <c r="F6">
-        <v>-1.095622068477412</v>
+        <v>-0.8656763895017003</v>
       </c>
       <c r="G6">
-        <v>-5.085230837176626</v>
+        <v>-4.327172187957692</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.395759623110425</v>
       </c>
       <c r="E7">
-        <v>-10.63335717885844</v>
+        <v>-9.712324435860394</v>
       </c>
       <c r="F7">
-        <v>-1.262104035622446</v>
+        <v>-0.9190282204464053</v>
       </c>
       <c r="G7">
-        <v>-4.64432907171095</v>
+        <v>-3.758708481772818</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.095880141587559</v>
       </c>
       <c r="E8">
-        <v>-12.22699963774177</v>
+        <v>-10.68842342279172</v>
       </c>
       <c r="F8">
-        <v>-1.365160395837329</v>
+        <v>-1.061479249236225</v>
       </c>
       <c r="G8">
-        <v>-3.89947287810263</v>
+        <v>-3.284863477645855</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.799703855509868</v>
       </c>
       <c r="E9">
-        <v>-12.95804931069602</v>
+        <v>-11.29714089890277</v>
       </c>
       <c r="F9">
-        <v>-1.273097299424998</v>
+        <v>-1.143090005760032</v>
       </c>
       <c r="G9">
-        <v>-3.496013382686111</v>
+        <v>-3.02338334877206</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.512275256116911</v>
       </c>
       <c r="E10">
-        <v>-13.72822952755056</v>
+        <v>-11.68536697558035</v>
       </c>
       <c r="F10">
-        <v>-1.646811111360981</v>
+        <v>-1.295262754389107</v>
       </c>
       <c r="G10">
-        <v>-3.039376594272279</v>
+        <v>-2.424346754532017</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.240603496053265</v>
       </c>
       <c r="E11">
-        <v>-13.09575567679527</v>
+        <v>-13.29306581778348</v>
       </c>
       <c r="F11">
-        <v>-1.572351650625542</v>
+        <v>-1.363242725299848</v>
       </c>
       <c r="G11">
-        <v>-2.367411992347631</v>
+        <v>-1.644706658942574</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.991393234077982</v>
       </c>
       <c r="E12">
-        <v>-14.56202574726485</v>
+        <v>-13.17833692879915</v>
       </c>
       <c r="F12">
-        <v>-1.374542485041437</v>
+        <v>-1.457917664133207</v>
       </c>
       <c r="G12">
-        <v>-1.951918663895861</v>
+        <v>-1.597468484642713</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.761709511139967</v>
       </c>
       <c r="E13">
-        <v>-15.59540540191919</v>
+        <v>-14.50306501568498</v>
       </c>
       <c r="F13">
-        <v>-1.387028466903834</v>
+        <v>-1.014669864038831</v>
       </c>
       <c r="G13">
-        <v>-1.81778860082675</v>
+        <v>-0.5273644339831555</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.553529533362599</v>
       </c>
       <c r="E14">
-        <v>-16.18410249444233</v>
+        <v>-15.17917977045219</v>
       </c>
       <c r="F14">
-        <v>-1.622330369506047</v>
+        <v>-1.18958378297696</v>
       </c>
       <c r="G14">
-        <v>-1.465020178707552</v>
+        <v>-0.1956279076749469</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.358084034493845</v>
       </c>
       <c r="E15">
-        <v>-17.33926640058496</v>
+        <v>-15.77555262641833</v>
       </c>
       <c r="F15">
-        <v>-1.23897187589927</v>
+        <v>-0.9416062023771086</v>
       </c>
       <c r="G15">
-        <v>-1.09141518296418</v>
+        <v>-0.5590794602493735</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.167061585929667</v>
       </c>
       <c r="E16">
-        <v>-17.450281940883</v>
+        <v>-16.78784770609296</v>
       </c>
       <c r="F16">
-        <v>-1.060414797123628</v>
+        <v>-0.7490165797980431</v>
       </c>
       <c r="G16">
-        <v>-0.6558500169078095</v>
+        <v>-0.01128680041170939</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.969852551172861</v>
       </c>
       <c r="E17">
-        <v>-18.58560207392401</v>
+        <v>-17.67780606045038</v>
       </c>
       <c r="F17">
-        <v>-0.8699134887670198</v>
+        <v>-0.6365549360917738</v>
       </c>
       <c r="G17">
-        <v>-0.5614465003099524</v>
+        <v>0.2023526348740781</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.755140504758966</v>
       </c>
       <c r="E18">
-        <v>-19.1955829942832</v>
+        <v>-18.04868808167858</v>
       </c>
       <c r="F18">
-        <v>-0.6912230428395272</v>
+        <v>-0.5302646295363609</v>
       </c>
       <c r="G18">
-        <v>0.2974513660351822</v>
+        <v>0.1102267736072395</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.52076871363964</v>
       </c>
       <c r="E19">
-        <v>-20.00232611027566</v>
+        <v>-19.18548449724609</v>
       </c>
       <c r="F19">
-        <v>0.01485745048910418</v>
+        <v>-0.333012126846937</v>
       </c>
       <c r="G19">
-        <v>0.495114108548447</v>
+        <v>1.294723414830774</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.265819369936084</v>
       </c>
       <c r="E20">
-        <v>-20.22236466230837</v>
+        <v>-19.46077948912039</v>
       </c>
       <c r="F20">
-        <v>-0.1816710590902729</v>
+        <v>0.03540179044593472</v>
       </c>
       <c r="G20">
-        <v>0.4352263397430312</v>
+        <v>0.8787632994579671</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.001199943310692</v>
       </c>
       <c r="E21">
-        <v>-21.71973629226262</v>
+        <v>-19.94880407597901</v>
       </c>
       <c r="F21">
-        <v>0.02801938015218552</v>
+        <v>0.5500913088273516</v>
       </c>
       <c r="G21">
-        <v>0.545580064749097</v>
+        <v>0.6505740165270827</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.739366931608061</v>
       </c>
       <c r="E22">
-        <v>-22.08360823572695</v>
+        <v>-20.55003598455538</v>
       </c>
       <c r="F22">
-        <v>0.5038427283616523</v>
+        <v>0.7374183132964317</v>
       </c>
       <c r="G22">
-        <v>0.3770931600734292</v>
+        <v>0.6813422267690691</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.498050429872537</v>
       </c>
       <c r="E23">
-        <v>-21.44281104974556</v>
+        <v>-21.11047087079665</v>
       </c>
       <c r="F23">
-        <v>0.8837858631666876</v>
+        <v>1.128687715599945</v>
       </c>
       <c r="G23">
-        <v>-0.04379635760735245</v>
+        <v>0.7649500543633629</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.296726275503809</v>
       </c>
       <c r="E24">
-        <v>-22.65508354159892</v>
+        <v>-22.49502915627182</v>
       </c>
       <c r="F24">
-        <v>1.120518356273536</v>
+        <v>1.354445997354505</v>
       </c>
       <c r="G24">
-        <v>-1.096404175091862</v>
+        <v>0.3198604487905089</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.153009141526693</v>
       </c>
       <c r="E25">
-        <v>-22.51482764463335</v>
+        <v>-22.19763521124009</v>
       </c>
       <c r="F25">
-        <v>1.332376633009121</v>
+        <v>1.339580115943865</v>
       </c>
       <c r="G25">
-        <v>-0.07209490087704255</v>
+        <v>0.04912403458891123</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.086542599569591</v>
       </c>
       <c r="E26">
-        <v>-22.78195779787182</v>
+        <v>-21.8413439332646</v>
       </c>
       <c r="F26">
-        <v>1.393720552656035</v>
+        <v>1.46325205571222</v>
       </c>
       <c r="G26">
-        <v>-0.7800981015421964</v>
+        <v>-0.5427816445595414</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.107826976329044</v>
       </c>
       <c r="E27">
-        <v>-22.74222043845451</v>
+        <v>-22.1493435644223</v>
       </c>
       <c r="F27">
-        <v>1.496378468150172</v>
+        <v>1.940837341387442</v>
       </c>
       <c r="G27">
-        <v>-1.533611371735711</v>
+        <v>-0.7210942483957661</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.224780440403123</v>
       </c>
       <c r="E28">
-        <v>-22.75835539134384</v>
+        <v>-21.75228696342976</v>
       </c>
       <c r="F28">
-        <v>1.64391235932357</v>
+        <v>2.014394710021232</v>
       </c>
       <c r="G28">
-        <v>-1.447067090248084</v>
+        <v>-1.309917809647157</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.433310669742203</v>
       </c>
       <c r="E29">
-        <v>-22.01697174070408</v>
+        <v>-21.9862822723541</v>
       </c>
       <c r="F29">
-        <v>1.647166186481766</v>
+        <v>1.690337382046065</v>
       </c>
       <c r="G29">
-        <v>-1.880543302069175</v>
+        <v>-1.578710933617203</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.725542734761982</v>
       </c>
       <c r="E30">
-        <v>-21.79139939343401</v>
+        <v>-21.28229023159567</v>
       </c>
       <c r="F30">
-        <v>2.035206612649167</v>
+        <v>1.742440034947349</v>
       </c>
       <c r="G30">
-        <v>-2.956404391421525</v>
+        <v>-1.875044485928445</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.084678078396869</v>
       </c>
       <c r="E31">
-        <v>-21.86343835794803</v>
+        <v>-20.99875341702742</v>
       </c>
       <c r="F31">
-        <v>1.663846192504537</v>
+        <v>2.206797949934668</v>
       </c>
       <c r="G31">
-        <v>-2.838403306219743</v>
+        <v>-1.83609260711338</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.488145913251145</v>
       </c>
       <c r="E32">
-        <v>-21.25504693196553</v>
+        <v>-20.35993517418738</v>
       </c>
       <c r="F32">
-        <v>1.623932137568046</v>
+        <v>1.787327607770248</v>
       </c>
       <c r="G32">
-        <v>-2.893811906910525</v>
+        <v>-2.597246616411533</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.912954847599292</v>
       </c>
       <c r="E33">
-        <v>-21.23654358717019</v>
+        <v>-21.251193200585</v>
       </c>
       <c r="F33">
-        <v>1.588426653949254</v>
+        <v>1.835415992237565</v>
       </c>
       <c r="G33">
-        <v>-3.191045927608449</v>
+        <v>-2.827193799023771</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.330557071964702</v>
       </c>
       <c r="E34">
-        <v>-20.92131198302225</v>
+        <v>-20.35613578449495</v>
       </c>
       <c r="F34">
-        <v>1.531430006432231</v>
+        <v>1.696187312644636</v>
       </c>
       <c r="G34">
-        <v>-2.411243615287582</v>
+        <v>-2.768345541517686</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.71744620957441</v>
       </c>
       <c r="E35">
-        <v>-20.36955365297968</v>
+        <v>-20.79753067449658</v>
       </c>
       <c r="F35">
-        <v>1.714118153445634</v>
+        <v>1.859958861647709</v>
       </c>
       <c r="G35">
-        <v>-2.97604916865156</v>
+        <v>-2.348548503864864</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.048302401247382</v>
       </c>
       <c r="E36">
-        <v>-19.95040262730371</v>
+        <v>-19.91797422493479</v>
       </c>
       <c r="F36">
-        <v>1.547790262637521</v>
+        <v>1.825724093624811</v>
       </c>
       <c r="G36">
-        <v>-3.029355572924905</v>
+        <v>-2.610065048739591</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.303138736758149</v>
       </c>
       <c r="E37">
-        <v>-18.95639805414606</v>
+        <v>-19.10240058462736</v>
       </c>
       <c r="F37">
-        <v>1.447234743611689</v>
+        <v>1.666405847779188</v>
       </c>
       <c r="G37">
-        <v>-2.714575660868843</v>
+        <v>-2.766925317481339</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.468583083141431</v>
       </c>
       <c r="E38">
-        <v>-19.68020669716206</v>
+        <v>-19.62982742382672</v>
       </c>
       <c r="F38">
-        <v>1.293390349563765</v>
+        <v>1.873756149108738</v>
       </c>
       <c r="G38">
-        <v>-3.715853469766953</v>
+        <v>-2.571526988116935</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.535915384281841</v>
       </c>
       <c r="E39">
-        <v>-19.0574373662052</v>
+        <v>-17.85117868783404</v>
       </c>
       <c r="F39">
-        <v>1.09471139820672</v>
+        <v>1.778971037410807</v>
       </c>
       <c r="G39">
-        <v>-2.214583968072716</v>
+        <v>-1.985653122941035</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.506231386643305</v>
       </c>
       <c r="E40">
-        <v>-17.28523717719944</v>
+        <v>-17.73317118366815</v>
       </c>
       <c r="F40">
-        <v>0.9185955181671284</v>
+        <v>1.511545875295431</v>
       </c>
       <c r="G40">
-        <v>-2.62982900560904</v>
+        <v>-2.093487522791715</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.384901213968655</v>
       </c>
       <c r="E41">
-        <v>-18.54690626352846</v>
+        <v>-17.45119669263254</v>
       </c>
       <c r="F41">
-        <v>1.040045776561175</v>
+        <v>1.174459984809034</v>
       </c>
       <c r="G41">
-        <v>-2.252109001760355</v>
+        <v>-2.043945208796522</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.184667461605347</v>
       </c>
       <c r="E42">
-        <v>-17.10855876379018</v>
+        <v>-17.33785351669456</v>
       </c>
       <c r="F42">
-        <v>0.8154985679495076</v>
+        <v>0.9743844060108695</v>
       </c>
       <c r="G42">
-        <v>-2.22537634653074</v>
+        <v>-2.166835969759807</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.924054115467525</v>
       </c>
       <c r="E43">
-        <v>-17.35873431034393</v>
+        <v>-16.86830963226125</v>
       </c>
       <c r="F43">
-        <v>0.6137314629148264</v>
+        <v>1.289810145648865</v>
       </c>
       <c r="G43">
-        <v>-2.42960390084838</v>
+        <v>-1.673945397145417</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.623186923187731</v>
       </c>
       <c r="E44">
-        <v>-17.17004185539232</v>
+        <v>-16.90820548826882</v>
       </c>
       <c r="F44">
-        <v>0.7525111673754388</v>
+        <v>0.9705159302397959</v>
       </c>
       <c r="G44">
-        <v>-2.266125851573629</v>
+        <v>-0.6610972315875543</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.305998994941624</v>
       </c>
       <c r="E45">
-        <v>-15.99048305977038</v>
+        <v>-14.83507461603134</v>
       </c>
       <c r="F45">
-        <v>0.6635693593368558</v>
+        <v>1.164842639262532</v>
       </c>
       <c r="G45">
-        <v>-1.752147103874081</v>
+        <v>-0.9010852988204012</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.992166894428142</v>
       </c>
       <c r="E46">
-        <v>-15.95333145901145</v>
+        <v>-14.47998791214189</v>
       </c>
       <c r="F46">
-        <v>0.5194268043105195</v>
+        <v>1.003508147158495</v>
       </c>
       <c r="G46">
-        <v>-2.189688665617397</v>
+        <v>-0.8325570061574876</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.697714398346738</v>
       </c>
       <c r="E47">
-        <v>-15.89924789393784</v>
+        <v>-15.13502262040339</v>
       </c>
       <c r="F47">
-        <v>0.3653289298373386</v>
+        <v>0.771523856004493</v>
       </c>
       <c r="G47">
-        <v>-1.285800485393567</v>
+        <v>-1.406817477581625</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.434882323993518</v>
       </c>
       <c r="E48">
-        <v>-14.03895982853488</v>
+        <v>-14.10136672883458</v>
       </c>
       <c r="F48">
-        <v>0.3873808984672643</v>
+        <v>0.7562040292571189</v>
       </c>
       <c r="G48">
-        <v>-1.258068045411092</v>
+        <v>-1.299201573736536</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.205772864928715</v>
       </c>
       <c r="E49">
-        <v>-14.20376458309602</v>
+        <v>-13.66081866347238</v>
       </c>
       <c r="F49">
-        <v>0.4556789624606807</v>
+        <v>0.6747788270315387</v>
       </c>
       <c r="G49">
-        <v>-1.469496036276646</v>
+        <v>-0.643501682046328</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.012902543464834</v>
       </c>
       <c r="E50">
-        <v>-14.11736582750368</v>
+        <v>-13.59275117066309</v>
       </c>
       <c r="F50">
-        <v>0.3002664689192571</v>
+        <v>0.4012792467514343</v>
       </c>
       <c r="G50">
-        <v>-1.973612668814706</v>
+        <v>-0.8096778259355845</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.850770407126169</v>
       </c>
       <c r="E51">
-        <v>-14.17387212617139</v>
+        <v>-12.4462909915632</v>
       </c>
       <c r="F51">
-        <v>0.4063099219886357</v>
+        <v>0.6493363506219547</v>
       </c>
       <c r="G51">
-        <v>-1.496745136610387</v>
+        <v>-1.382230055861458</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.714074659250223</v>
       </c>
       <c r="E52">
-        <v>-12.84942027620003</v>
+        <v>-12.34238515545721</v>
       </c>
       <c r="F52">
-        <v>0.2323660212791844</v>
+        <v>0.2782194704937482</v>
       </c>
       <c r="G52">
-        <v>-1.74624440117756</v>
+        <v>-1.731048997152306</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.596513404408126</v>
       </c>
       <c r="E53">
-        <v>-13.1441831778333</v>
+        <v>-12.80030444711283</v>
       </c>
       <c r="F53">
-        <v>0.1428236468735718</v>
+        <v>0.6310534536747668</v>
       </c>
       <c r="G53">
-        <v>-2.130608669923563</v>
+        <v>-1.10758719792352</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.489871789449733</v>
       </c>
       <c r="E54">
-        <v>-12.29383085714696</v>
+        <v>-11.56813384046978</v>
       </c>
       <c r="F54">
-        <v>0.1888949567150719</v>
+        <v>0.8728480999801229</v>
       </c>
       <c r="G54">
-        <v>-2.846520763882036</v>
+        <v>-2.441419237878038</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.391885377703501</v>
       </c>
       <c r="E55">
-        <v>-12.1145530996573</v>
+        <v>-11.33012630357464</v>
       </c>
       <c r="F55">
-        <v>0.1762921750488802</v>
+        <v>0.5418266872496209</v>
       </c>
       <c r="G55">
-        <v>-2.250596082448908</v>
+        <v>-1.795902584266628</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.298761548346302</v>
       </c>
       <c r="E56">
-        <v>-11.42133429856313</v>
+        <v>-10.9208518797094</v>
       </c>
       <c r="F56">
-        <v>-0.03163384162561527</v>
+        <v>0.358026871181661</v>
       </c>
       <c r="G56">
-        <v>-2.765223697074153</v>
+        <v>-1.975324220858509</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.212968472358933</v>
       </c>
       <c r="E57">
-        <v>-12.26488485128994</v>
+        <v>-11.15736954865602</v>
       </c>
       <c r="F57">
-        <v>-0.1036454766857819</v>
+        <v>0.3417519368188591</v>
       </c>
       <c r="G57">
-        <v>-3.355295333993849</v>
+        <v>-2.280933921770789</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.136137528492028</v>
       </c>
       <c r="E58">
-        <v>-11.51896366969449</v>
+        <v>-9.977815281508084</v>
       </c>
       <c r="F58">
-        <v>0.1042217259031148</v>
+        <v>0.414968846450099</v>
       </c>
       <c r="G58">
-        <v>-3.275494633769718</v>
+        <v>-2.847795323914655</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.071603005696596</v>
       </c>
       <c r="E59">
-        <v>-11.6848099732774</v>
+        <v>-10.55615122550167</v>
       </c>
       <c r="F59">
-        <v>0.007880111855323944</v>
+        <v>0.5328546399098995</v>
       </c>
       <c r="G59">
-        <v>-3.536792682638853</v>
+        <v>-3.123020837867505</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.022960183752732</v>
       </c>
       <c r="E60">
-        <v>-11.34420532926448</v>
+        <v>-9.893313956524954</v>
       </c>
       <c r="F60">
-        <v>-0.03009307825640819</v>
+        <v>0.4332807362563849</v>
       </c>
       <c r="G60">
-        <v>-3.553140156511774</v>
+        <v>-3.23196758101938</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.989978694649715</v>
       </c>
       <c r="E61">
-        <v>-11.31426305912577</v>
+        <v>-10.17710889411165</v>
       </c>
       <c r="F61">
-        <v>-0.200626590368534</v>
+        <v>0.8775681374412745</v>
       </c>
       <c r="G61">
-        <v>-4.465486780588442</v>
+        <v>-3.63755906776319</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.973108686582184</v>
       </c>
       <c r="E62">
-        <v>-10.19660850318868</v>
+        <v>-9.19787167469301</v>
       </c>
       <c r="F62">
-        <v>-0.181484676424643</v>
+        <v>0.6206350768497575</v>
       </c>
       <c r="G62">
-        <v>-4.172533295272795</v>
+        <v>-3.340821628896156</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.967662282068366</v>
       </c>
       <c r="E63">
-        <v>-10.49547873074691</v>
+        <v>-9.35635467953945</v>
       </c>
       <c r="F63">
-        <v>0.07374526078671824</v>
+        <v>0.2574821209320654</v>
       </c>
       <c r="G63">
-        <v>-4.836632040996135</v>
+        <v>-3.619317961841805</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.969784237908456</v>
       </c>
       <c r="E64">
-        <v>-10.14905952610814</v>
+        <v>-9.320815215527253</v>
       </c>
       <c r="F64">
-        <v>-0.2505059051607034</v>
+        <v>0.6085392560340791</v>
       </c>
       <c r="G64">
-        <v>-4.542480138195272</v>
+        <v>-3.664106332442605</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.974961298698576</v>
       </c>
       <c r="E65">
-        <v>-10.26379747204048</v>
+        <v>-7.868814366655845</v>
       </c>
       <c r="F65">
-        <v>-0.1630965768172996</v>
+        <v>0.4108675994388387</v>
       </c>
       <c r="G65">
-        <v>-4.92413969123569</v>
+        <v>-3.695056622689251</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.978718430903875</v>
       </c>
       <c r="E66">
-        <v>-10.77169300284476</v>
+        <v>-8.981211364270029</v>
       </c>
       <c r="F66">
-        <v>-0.05849862486580604</v>
+        <v>0.2844131735644801</v>
       </c>
       <c r="G66">
-        <v>-5.070071849152304</v>
+        <v>-4.528152097101306</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.978944260324412</v>
       </c>
       <c r="E67">
-        <v>-10.43978755740058</v>
+        <v>-8.649192706975654</v>
       </c>
       <c r="F67">
-        <v>-0.2139202304486605</v>
+        <v>0.2794123195537795</v>
       </c>
       <c r="G67">
-        <v>-4.914770847359553</v>
+        <v>-4.279050097998846</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.97158336560577</v>
       </c>
       <c r="E68">
-        <v>-9.636957042950737</v>
+        <v>-8.782388712963263</v>
       </c>
       <c r="F68">
-        <v>-0.4034896254771189</v>
+        <v>0.3155341085202547</v>
       </c>
       <c r="G68">
-        <v>-5.133157604948655</v>
+        <v>-4.274375607697395</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.955701777691708</v>
       </c>
       <c r="E69">
-        <v>-10.48999022024961</v>
+        <v>-8.670911268316441</v>
       </c>
       <c r="F69">
-        <v>-0.5556300677774846</v>
+        <v>0.2444535584208347</v>
       </c>
       <c r="G69">
-        <v>-5.028266280082387</v>
+        <v>-4.654634799974701</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.930005012257778</v>
       </c>
       <c r="E70">
-        <v>-10.99706156878449</v>
+        <v>-9.232668468967949</v>
       </c>
       <c r="F70">
-        <v>-0.5048643998643196</v>
+        <v>-0.07895764298014823</v>
       </c>
       <c r="G70">
-        <v>-5.745168227157102</v>
+        <v>-4.749515035130214</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.895381978709041</v>
       </c>
       <c r="E71">
-        <v>-10.35466130300439</v>
+        <v>-8.676119013425263</v>
       </c>
       <c r="F71">
-        <v>-0.4285875010471384</v>
+        <v>0.09256411144351741</v>
       </c>
       <c r="G71">
-        <v>-4.874703314697753</v>
+        <v>-4.273024905117373</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.853365590875591</v>
       </c>
       <c r="E72">
-        <v>-10.12291211718785</v>
+        <v>-8.787696084500253</v>
       </c>
       <c r="F72">
-        <v>-0.2414269984260209</v>
+        <v>0.1874834186607016</v>
       </c>
       <c r="G72">
-        <v>-5.481619007321262</v>
+        <v>-4.472250225125173</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.803959062260834</v>
       </c>
       <c r="E73">
-        <v>-9.64363654211205</v>
+        <v>-9.389897086514264</v>
       </c>
       <c r="F73">
-        <v>-0.5533056688452291</v>
+        <v>0.1972382731960685</v>
       </c>
       <c r="G73">
-        <v>-5.355192583722034</v>
+        <v>-3.909186018714851</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.749070014769729</v>
       </c>
       <c r="E74">
-        <v>-10.70947629845338</v>
+        <v>-8.975288120267997</v>
       </c>
       <c r="F74">
-        <v>-0.4013830871717998</v>
+        <v>-0.1034143621804008</v>
       </c>
       <c r="G74">
-        <v>-5.228981345582859</v>
+        <v>-4.112681942468312</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.687223622946398</v>
       </c>
       <c r="E75">
-        <v>-11.66933164911918</v>
+        <v>-9.130945357333651</v>
       </c>
       <c r="F75">
-        <v>-0.4487971805732379</v>
+        <v>0.03687297095330664</v>
       </c>
       <c r="G75">
-        <v>-4.535574340200353</v>
+        <v>-4.229620342551988</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.617019992367932</v>
       </c>
       <c r="E76">
-        <v>-11.31035045758314</v>
+        <v>-9.351789977739719</v>
       </c>
       <c r="F76">
-        <v>-0.5511759362526316</v>
+        <v>-0.02130161501049704</v>
       </c>
       <c r="G76">
-        <v>-4.573857488816484</v>
+        <v>-4.317194203702329</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.536887474201277</v>
       </c>
       <c r="E77">
-        <v>-11.54054637681505</v>
+        <v>-10.35103852379825</v>
       </c>
       <c r="F77">
-        <v>-0.6297606666540123</v>
+        <v>-0.2742775645188408</v>
       </c>
       <c r="G77">
-        <v>-4.019986667368719</v>
+        <v>-3.920574295369944</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.44367377444183</v>
       </c>
       <c r="E78">
-        <v>-12.26671888326304</v>
+        <v>-10.18039203776721</v>
       </c>
       <c r="F78">
-        <v>-0.4298018876596424</v>
+        <v>-0.2089690784821278</v>
       </c>
       <c r="G78">
-        <v>-4.148290170288712</v>
+        <v>-3.43015007918231</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.337114210003041</v>
       </c>
       <c r="E79">
-        <v>-12.69043461073874</v>
+        <v>-10.60249562849617</v>
       </c>
       <c r="F79">
-        <v>-0.3586103363282473</v>
+        <v>-0.4485229909629113</v>
       </c>
       <c r="G79">
-        <v>-4.299515890522621</v>
+        <v>-3.812051302047095</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.214304230200531</v>
       </c>
       <c r="E80">
-        <v>-12.78879759465934</v>
+        <v>-12.25563770736627</v>
       </c>
       <c r="F80">
-        <v>-0.7568140021605949</v>
+        <v>-0.2822274064835077</v>
       </c>
       <c r="G80">
-        <v>-4.300909630194654</v>
+        <v>-3.60798596446088</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.075058698272279</v>
       </c>
       <c r="E81">
-        <v>-14.37469636298955</v>
+        <v>-12.05926496049766</v>
       </c>
       <c r="F81">
-        <v>-0.89959803464634</v>
+        <v>-0.4160766681626574</v>
       </c>
       <c r="G81">
-        <v>-4.276325519020026</v>
+        <v>-3.489524713429139</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.919967870326954</v>
       </c>
       <c r="E82">
-        <v>-14.50248989948601</v>
+        <v>-13.1019732716078</v>
       </c>
       <c r="F82">
-        <v>-0.5887697340938816</v>
+        <v>0.01731935841022431</v>
       </c>
       <c r="G82">
-        <v>-3.699727802445163</v>
+        <v>-3.782213355101644</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.751220077212094</v>
       </c>
       <c r="E83">
-        <v>-15.31826732112378</v>
+        <v>-13.78933675581006</v>
       </c>
       <c r="F83">
-        <v>-1.09961894119592</v>
+        <v>-0.4494822404153531</v>
       </c>
       <c r="G83">
-        <v>-4.089220106231497</v>
+        <v>-2.886048677620934</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.574757190445996</v>
       </c>
       <c r="E84">
-        <v>-16.14551536742297</v>
+        <v>-14.90503501097584</v>
       </c>
       <c r="F84">
-        <v>-1.086257374988764</v>
+        <v>-0.6614747126701914</v>
       </c>
       <c r="G84">
-        <v>-3.257889152591873</v>
+        <v>-2.417053622709002</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.395729391034082</v>
       </c>
       <c r="E85">
-        <v>-16.8597236455427</v>
+        <v>-15.80592963006178</v>
       </c>
       <c r="F85">
-        <v>-1.208933617138954</v>
+        <v>-0.6790037952808317</v>
       </c>
       <c r="G85">
-        <v>-3.784646606073008</v>
+        <v>-3.015987590037328</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.223757909204274</v>
       </c>
       <c r="E86">
-        <v>-18.4595519999205</v>
+        <v>-17.55843548560819</v>
       </c>
       <c r="F86">
-        <v>-1.339858741886221</v>
+        <v>-0.7492228432813403</v>
       </c>
       <c r="G86">
-        <v>-3.86095137020767</v>
+        <v>-2.306041099140622</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.06718607152109</v>
       </c>
       <c r="E87">
-        <v>-19.47650235087502</v>
+        <v>-17.94418901547758</v>
       </c>
       <c r="F87">
-        <v>-1.110768766437601</v>
+        <v>-0.5872985535865096</v>
       </c>
       <c r="G87">
-        <v>-2.943324425995864</v>
+        <v>-3.399289173665224</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.935499186463085</v>
       </c>
       <c r="E88">
-        <v>-20.57917671479474</v>
+        <v>-19.77094825932775</v>
       </c>
       <c r="F88">
-        <v>-1.233799549836189</v>
+        <v>-0.7451961493363318</v>
       </c>
       <c r="G88">
-        <v>-2.896361026975764</v>
+        <v>-2.198637070210047</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.836925410181776</v>
       </c>
       <c r="E89">
-        <v>-22.38743261384957</v>
+        <v>-21.22930708570593</v>
       </c>
       <c r="F89">
-        <v>-1.302228495879248</v>
+        <v>-0.8720838113623545</v>
       </c>
       <c r="G89">
-        <v>-3.178273842917941</v>
+        <v>-2.385480949900973</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.776770677394424</v>
       </c>
       <c r="E90">
-        <v>-23.8877975651229</v>
+        <v>-23.25107147727441</v>
       </c>
       <c r="F90">
-        <v>-1.321787078626747</v>
+        <v>-1.168297225827221</v>
       </c>
       <c r="G90">
-        <v>-2.941695637590543</v>
+        <v>-2.318250391089454</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.759635660456065</v>
       </c>
       <c r="E91">
-        <v>-25.8304676296734</v>
+        <v>-24.61511577549484</v>
       </c>
       <c r="F91">
-        <v>-1.560555698809677</v>
+        <v>-1.03686514022944</v>
       </c>
       <c r="G91">
-        <v>-3.587576451211273</v>
+        <v>-3.067787696090304</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.785193887445276</v>
       </c>
       <c r="E92">
-        <v>-27.13951361107068</v>
+        <v>-27.20687013346076</v>
       </c>
       <c r="F92">
-        <v>-1.766462155756147</v>
+        <v>-1.28982203728752</v>
       </c>
       <c r="G92">
-        <v>-3.554315400178215</v>
+        <v>-2.845031018389364</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.853427194569377</v>
       </c>
       <c r="E93">
-        <v>-29.07856089641504</v>
+        <v>-28.5349085348462</v>
       </c>
       <c r="F93">
-        <v>-1.577861950588964</v>
+        <v>-1.105166517692468</v>
       </c>
       <c r="G93">
-        <v>-4.150607552166202</v>
+        <v>-2.841465560843569</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.960087654619298</v>
       </c>
       <c r="E94">
-        <v>-30.93169170864889</v>
+        <v>-30.12976462476358</v>
       </c>
       <c r="F94">
-        <v>-1.781315611655745</v>
+        <v>-1.24454678852011</v>
       </c>
       <c r="G94">
-        <v>-3.536186852805166</v>
+        <v>-3.205549427615996</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.10210495480728</v>
       </c>
       <c r="E95">
-        <v>-32.95680264250903</v>
+        <v>-32.83569766212191</v>
       </c>
       <c r="F95">
-        <v>-1.939729280297511</v>
+        <v>-1.522802026059687</v>
       </c>
       <c r="G95">
-        <v>-4.289514732448482</v>
+        <v>-3.511086296526412</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.280421038347792</v>
       </c>
       <c r="E96">
-        <v>-35.05766362533249</v>
+        <v>-35.58984309800289</v>
       </c>
       <c r="F96">
-        <v>-1.935966835553996</v>
+        <v>-1.614977780438799</v>
       </c>
       <c r="G96">
-        <v>-4.458511461137197</v>
+        <v>-3.762462640414352</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.488307680475898</v>
       </c>
       <c r="E97">
-        <v>-37.76560504091321</v>
+        <v>-37.45785900429996</v>
       </c>
       <c r="F97">
-        <v>-2.144093317139969</v>
+        <v>-1.959018643639101</v>
       </c>
       <c r="G97">
-        <v>-4.777598392939852</v>
+        <v>-3.922160046683255</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.73966124695618</v>
       </c>
       <c r="E98">
-        <v>-40.31604386627016</v>
+        <v>-40.33953306094795</v>
       </c>
       <c r="F98">
-        <v>-2.362007787957421</v>
+        <v>-1.610131831132422</v>
       </c>
       <c r="G98">
-        <v>-4.751309350812499</v>
+        <v>-4.49529493262404</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.018484917925907</v>
       </c>
       <c r="E99">
-        <v>-42.70831441572421</v>
+        <v>-43.54425486788113</v>
       </c>
       <c r="F99">
-        <v>-2.451372891738834</v>
+        <v>-2.013415045878736</v>
       </c>
       <c r="G99">
-        <v>-5.511688692454462</v>
+        <v>-4.818486940895389</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.357258479559625</v>
       </c>
       <c r="E100">
-        <v>-44.95640740972204</v>
+        <v>-45.65810124992157</v>
       </c>
       <c r="F100">
-        <v>-2.502333225991657</v>
+        <v>-2.066913497853736</v>
       </c>
       <c r="G100">
-        <v>-5.653231066986002</v>
+        <v>-4.174016419674389</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.710113331031499</v>
       </c>
       <c r="E101">
-        <v>-47.07790917707246</v>
+        <v>-47.29392870842335</v>
       </c>
       <c r="F101">
-        <v>-2.877293730868853</v>
+        <v>-2.37329015198355</v>
       </c>
       <c r="G101">
-        <v>-5.628176858344797</v>
+        <v>-5.170705812455069</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.15001791663477</v>
       </c>
       <c r="E102">
-        <v>-49.55780343433791</v>
+        <v>-49.94249277281551</v>
       </c>
       <c r="F102">
-        <v>-3.069962048351185</v>
+        <v>-2.688387858130037</v>
       </c>
       <c r="G102">
-        <v>-5.955318347444497</v>
+        <v>-5.400732448160249</v>
       </c>
     </row>
   </sheetData>
